--- a/Team-Data/2013-14/4-10-2013-14.xlsx
+++ b/Team-Data/2013-14/4-10-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE3" t="n">
         <v>27</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE4" t="n">
         <v>14</v>
@@ -1160,7 +1227,7 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
         <v>28</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE5" t="n">
         <v>15</v>
@@ -1351,7 +1418,7 @@
         <v>21</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA5" t="n">
         <v>9</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -1467,13 +1534,13 @@
         <v>1.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE6" t="n">
         <v>11</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>21</v>
@@ -1718,7 +1785,7 @@
         <v>9</v>
       </c>
       <c r="BA7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB7" t="n">
         <v>22</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" t="n">
         <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>0.608</v>
       </c>
       <c r="H8" t="n">
         <v>48.3</v>
@@ -1774,13 +1841,13 @@
         <v>83.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="L8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N8" t="n">
         <v>0.385</v>
@@ -1810,16 +1877,16 @@
         <v>13.5</v>
       </c>
       <c r="W8" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X8" t="n">
         <v>4.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA8" t="n">
         <v>20</v>
@@ -1828,7 +1895,7 @@
         <v>104.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
@@ -1837,10 +1904,10 @@
         <v>8</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
         <v>20</v>
@@ -1888,7 +1955,7 @@
         <v>3</v>
       </c>
       <c r="AW8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
         <v>21</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F9" t="n">
         <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>0.443</v>
+        <v>0.436</v>
       </c>
       <c r="H9" t="n">
         <v>48.2</v>
@@ -1953,37 +2020,37 @@
         <v>38.5</v>
       </c>
       <c r="J9" t="n">
-        <v>86</v>
+        <v>85.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L9" t="n">
         <v>8.6</v>
       </c>
       <c r="M9" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O9" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P9" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.72</v>
+        <v>0.721</v>
       </c>
       <c r="R9" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S9" t="n">
         <v>33.1</v>
       </c>
       <c r="T9" t="n">
-        <v>45.4</v>
+        <v>45.2</v>
       </c>
       <c r="U9" t="n">
         <v>22.4</v>
@@ -1995,28 +2062,28 @@
         <v>7.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
         <v>21.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>104.3</v>
+        <v>104.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF9" t="n">
         <v>19</v>
@@ -2025,7 +2092,7 @@
         <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
         <v>12</v>
@@ -2034,7 +2101,7 @@
         <v>5</v>
       </c>
       <c r="AK9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL9" t="n">
         <v>10</v>
@@ -2061,7 +2128,7 @@
         <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AU9" t="n">
         <v>12</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2243,7 +2310,7 @@
         <v>21</v>
       </c>
       <c r="AT10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2366,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E11" t="n">
         <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
-        <v>0.615</v>
+        <v>0.623</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J11" t="n">
         <v>85</v>
@@ -2323,22 +2390,22 @@
         <v>0.461</v>
       </c>
       <c r="L11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M11" t="n">
         <v>24.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O11" t="n">
         <v>16</v>
       </c>
       <c r="P11" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R11" t="n">
         <v>10.9</v>
@@ -2347,10 +2414,10 @@
         <v>34.3</v>
       </c>
       <c r="T11" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="U11" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V11" t="n">
         <v>15.2</v>
@@ -2368,16 +2435,16 @@
         <v>21.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.5</v>
+        <v>103.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2410,7 +2477,7 @@
         <v>5</v>
       </c>
       <c r="AO11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP11" t="n">
         <v>24</v>
@@ -2419,22 +2486,22 @@
         <v>19</v>
       </c>
       <c r="AR11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
         <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX11" t="n">
         <v>10</v>
@@ -2446,13 +2513,13 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB11" t="n">
         <v>10</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>4.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
@@ -2607,7 +2674,7 @@
         <v>3</v>
       </c>
       <c r="AT12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="n">
         <v>18</v>
@@ -2634,7 +2701,7 @@
         <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>4</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2935,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2947,7 +3014,7 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3174,7 +3241,7 @@
         <v>11</v>
       </c>
       <c r="BA15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BB15" t="n">
         <v>11</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -3287,13 +3354,13 @@
         <v>1.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
       </c>
       <c r="AF16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>3</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE19" t="n">
         <v>17</v>
@@ -3845,7 +3912,7 @@
         <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI19" t="n">
         <v>7</v>
@@ -3899,7 +3966,7 @@
         <v>24</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
         <v>21</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
@@ -4218,7 +4285,7 @@
         <v>16</v>
       </c>
       <c r="AK21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL21" t="n">
         <v>6</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
         <v>5</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-5.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE23" t="n">
         <v>27</v>
@@ -4594,7 +4661,7 @@
         <v>20</v>
       </c>
       <c r="AO23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP23" t="n">
         <v>25</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-10.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4934,7 +5001,7 @@
         <v>9</v>
       </c>
       <c r="AG25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>24</v>
@@ -4973,7 +5040,7 @@
         <v>16</v>
       </c>
       <c r="AT25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU25" t="n">
         <v>29</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>3.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -5393,37 +5460,37 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E28" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F28" t="n">
         <v>18</v>
       </c>
       <c r="G28" t="n">
-        <v>0.772</v>
+        <v>0.769</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
       </c>
       <c r="I28" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="J28" t="n">
         <v>83</v>
       </c>
       <c r="K28" t="n">
-        <v>0.488</v>
+        <v>0.489</v>
       </c>
       <c r="L28" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.399</v>
+        <v>0.398</v>
       </c>
       <c r="O28" t="n">
         <v>15.8</v>
@@ -5432,10 +5499,10 @@
         <v>20.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="R28" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S28" t="n">
         <v>33.9</v>
@@ -5447,7 +5514,7 @@
         <v>25.2</v>
       </c>
       <c r="V28" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W28" t="n">
         <v>7.4</v>
@@ -5462,16 +5529,16 @@
         <v>18.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB28" t="n">
         <v>105.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5495,7 +5562,7 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM28" t="n">
         <v>17</v>
@@ -5519,7 +5586,7 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5537,10 +5604,10 @@
         <v>16</v>
       </c>
       <c r="AZ28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BB28" t="n">
         <v>7</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
       </c>
       <c r="AF29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG29" t="n">
         <v>11</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-7.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE30" t="n">
         <v>26</v>
@@ -5877,7 +5944,7 @@
         <v>22</v>
       </c>
       <c r="AR30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS30" t="n">
         <v>26</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6059,7 +6126,7 @@
         <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS31" t="n">
         <v>17</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-10-2013-14</t>
+          <t>2014-04-10</t>
         </is>
       </c>
     </row>
